--- a/public/downloads/RolingConfigurational2017.xlsx
+++ b/public/downloads/RolingConfigurational2017.xlsx
@@ -8,14 +8,16 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="40">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -47,10 +49,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
-  </si>
-  <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_total (ms)</t>
+  </si>
+  <si>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -620,10 +622,10 @@
         <v>104</v>
       </c>
       <c r="N3" s="5">
-        <v>200.9520864486694</v>
+        <v>200952.0864486694</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03084926104523633</v>
+        <v>30.84926104523633</v>
       </c>
       <c r="P3" s="5">
         <v>6514</v>
@@ -670,10 +672,10 @@
         <v>104</v>
       </c>
       <c r="N4" s="5">
-        <v>405.7869956493378</v>
+        <v>405786.9956493378</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04430472711533331</v>
+        <v>44.30472711533331</v>
       </c>
       <c r="P4" s="5">
         <v>9159</v>
@@ -720,10 +722,10 @@
         <v>104</v>
       </c>
       <c r="N5" s="5">
-        <v>1016.029210090637</v>
+        <v>1016029.210090637</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1600550110413732</v>
+        <v>160.0550110413732</v>
       </c>
       <c r="P5" s="5">
         <v>6348</v>
@@ -770,10 +772,10 @@
         <v>104</v>
       </c>
       <c r="N6" s="5">
-        <v>633.7478663921356</v>
+        <v>633747.8663921356</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08473697906032031</v>
+        <v>84.73697906032031</v>
       </c>
       <c r="P6" s="5">
         <v>7479</v>
@@ -820,10 +822,10 @@
         <v>104</v>
       </c>
       <c r="N7" s="5">
-        <v>796.9503824710846</v>
+        <v>796950.3824710846</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1561423163148677</v>
+        <v>156.1423163148677</v>
       </c>
       <c r="P7" s="5">
         <v>5104</v>
@@ -870,10 +872,10 @@
         <v>104</v>
       </c>
       <c r="N8" s="5">
-        <v>75.6194908618927</v>
+        <v>75619.4908618927</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01241087983947033</v>
+        <v>12.41087983947033</v>
       </c>
       <c r="P8" s="5">
         <v>6093</v>
@@ -920,10 +922,10 @@
         <v>104</v>
       </c>
       <c r="N9" s="5">
-        <v>217.7392194271088</v>
+        <v>217739.2194271088</v>
       </c>
       <c r="O9" s="4">
-        <v>0.028574700712219</v>
+        <v>28.574700712219</v>
       </c>
       <c r="P9" s="5">
         <v>7620</v>
@@ -970,10 +972,10 @@
         <v>104</v>
       </c>
       <c r="N10" s="5">
-        <v>585.1411719322205</v>
+        <v>585141.1719322205</v>
       </c>
       <c r="O10" s="4">
-        <v>0.0880971351900362</v>
+        <v>88.0971351900362</v>
       </c>
       <c r="P10" s="5">
         <v>6642</v>
@@ -1020,10 +1022,10 @@
         <v>104</v>
       </c>
       <c r="N11" s="5">
-        <v>263.6161639690399</v>
+        <v>263616.1639690399</v>
       </c>
       <c r="O11" s="4">
-        <v>0.03845043231753791</v>
+        <v>38.45043231753791</v>
       </c>
       <c r="P11" s="5">
         <v>6856</v>
@@ -1070,10 +1072,10 @@
         <v>104</v>
       </c>
       <c r="N12" s="5">
-        <v>131.9437901973724</v>
+        <v>131943.7901973724</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01760424152066343</v>
+        <v>17.60424152066343</v>
       </c>
       <c r="P12" s="5">
         <v>7495</v>
@@ -1120,10 +1122,10 @@
         <v>104</v>
       </c>
       <c r="N13" s="5">
-        <v>409.2289431095123</v>
+        <v>409228.9431095123</v>
       </c>
       <c r="O13" s="4">
-        <v>0.0724042716046554</v>
+        <v>72.40427160465541</v>
       </c>
       <c r="P13" s="5">
         <v>5652</v>
@@ -1151,6 +1153,663 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>100</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.103021916988827</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.103021916988827</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.1060186066048415</v>
+      </c>
+      <c r="K3" s="4">
+        <v>86.07993197278911</v>
+      </c>
+      <c r="L3" s="4">
+        <v>90.96551798313544</v>
+      </c>
+      <c r="M3" s="5">
+        <v>104</v>
+      </c>
+      <c r="N3" s="5">
+        <v>200952.0864486694</v>
+      </c>
+      <c r="O3" s="4">
+        <v>30.84926104523633</v>
+      </c>
+      <c r="P3" s="5">
+        <v>6514</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>100</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.1140993187405174</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.1140993187405174</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.1174083778488327</v>
+      </c>
+      <c r="K4" s="4">
+        <v>80.64887493458922</v>
+      </c>
+      <c r="L4" s="4">
+        <v>86.32184649802096</v>
+      </c>
+      <c r="M4" s="5">
+        <v>104</v>
+      </c>
+      <c r="N4" s="5">
+        <v>405786.9956493378</v>
+      </c>
+      <c r="O4" s="4">
+        <v>44.30472711533331</v>
+      </c>
+      <c r="P4" s="5">
+        <v>9159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>100</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.05831450248664646</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.05831450248664646</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.06160941940857922</v>
+      </c>
+      <c r="K5" s="4">
+        <v>85.13343799058082</v>
+      </c>
+      <c r="L5" s="4">
+        <v>90.6692049561177</v>
+      </c>
+      <c r="M5" s="5">
+        <v>104</v>
+      </c>
+      <c r="N5" s="5">
+        <v>1016029.210090637</v>
+      </c>
+      <c r="O5" s="4">
+        <v>160.0550110413732</v>
+      </c>
+      <c r="P5" s="5">
+        <v>6348</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>100</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.1372351381088362</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.1372351381088362</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.1164844112913922</v>
+      </c>
+      <c r="K6" s="4">
+        <v>84.63108320251176</v>
+      </c>
+      <c r="L6" s="4">
+        <v>89.35209086215797</v>
+      </c>
+      <c r="M6" s="5">
+        <v>104</v>
+      </c>
+      <c r="N6" s="5">
+        <v>633747.8663921356</v>
+      </c>
+      <c r="O6" s="4">
+        <v>84.73697906032031</v>
+      </c>
+      <c r="P6" s="5">
+        <v>7479</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>100</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.0478067333306197</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.0478067333306197</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.04939457123855819</v>
+      </c>
+      <c r="K7" s="4">
+        <v>88.9046964939822</v>
+      </c>
+      <c r="L7" s="4">
+        <v>92.65767509895028</v>
+      </c>
+      <c r="M7" s="5">
+        <v>104</v>
+      </c>
+      <c r="N7" s="5">
+        <v>796950.3824710846</v>
+      </c>
+      <c r="O7" s="4">
+        <v>156.1423163148677</v>
+      </c>
+      <c r="P7" s="5">
+        <v>5104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>100</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.09964046277429914</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.09964046277429914</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.1035194106231965</v>
+      </c>
+      <c r="K8" s="4">
+        <v>86.36087127158555</v>
+      </c>
+      <c r="L8" s="4">
+        <v>91.02123128549302</v>
+      </c>
+      <c r="M8" s="5">
+        <v>104</v>
+      </c>
+      <c r="N8" s="5">
+        <v>75619.4908618927</v>
+      </c>
+      <c r="O8" s="4">
+        <v>12.41087983947033</v>
+      </c>
+      <c r="P8" s="5">
+        <v>6093</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>98.07692307692307</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1.923076923076923</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1.923076923076923</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.1095421811633829</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.1077199527352652</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.1015031107460929</v>
+      </c>
+      <c r="K9" s="4">
+        <v>86.20290423861852</v>
+      </c>
+      <c r="L9" s="4">
+        <v>89.95622526243322</v>
+      </c>
+      <c r="M9" s="5">
+        <v>104</v>
+      </c>
+      <c r="N9" s="5">
+        <v>217739.2194271088</v>
+      </c>
+      <c r="O9" s="4">
+        <v>28.574700712219</v>
+      </c>
+      <c r="P9" s="5">
+        <v>7620</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>100</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.08055680187672976</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.08055680187672976</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.07785016243543508</v>
+      </c>
+      <c r="K10" s="4">
+        <v>84.19250392464679</v>
+      </c>
+      <c r="L10" s="4">
+        <v>89.80801497160557</v>
+      </c>
+      <c r="M10" s="5">
+        <v>104</v>
+      </c>
+      <c r="N10" s="5">
+        <v>585141.1719322205</v>
+      </c>
+      <c r="O10" s="4">
+        <v>88.0971351900362</v>
+      </c>
+      <c r="P10" s="5">
+        <v>6642</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>100</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.1319909119088531</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.1319909119088531</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.1383613676439696</v>
+      </c>
+      <c r="K11" s="4">
+        <v>86.07110151753011</v>
+      </c>
+      <c r="L11" s="4">
+        <v>90.10185424195491</v>
+      </c>
+      <c r="M11" s="5">
+        <v>104</v>
+      </c>
+      <c r="N11" s="5">
+        <v>263616.1639690399</v>
+      </c>
+      <c r="O11" s="4">
+        <v>38.45043231753791</v>
+      </c>
+      <c r="P11" s="5">
+        <v>6856</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>100</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.08673320255060089</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.08673320255060089</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.08540929730643801</v>
+      </c>
+      <c r="K12" s="4">
+        <v>81.09399529042385</v>
+      </c>
+      <c r="L12" s="4">
+        <v>87.67983135432802</v>
+      </c>
+      <c r="M12" s="5">
+        <v>104</v>
+      </c>
+      <c r="N12" s="5">
+        <v>131943.7901973724</v>
+      </c>
+      <c r="O12" s="4">
+        <v>17.60424152066343</v>
+      </c>
+      <c r="P12" s="5">
+        <v>7495</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>100</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.06454059049285941</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.06454059049285941</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.06561969954937533</v>
+      </c>
+      <c r="K13" s="4">
+        <v>87.70408163265306</v>
+      </c>
+      <c r="L13" s="4">
+        <v>91.93200395801065</v>
+      </c>
+      <c r="M13" s="5">
+        <v>104</v>
+      </c>
+      <c r="N13" s="5">
+        <v>409228.9431095123</v>
+      </c>
+      <c r="O13" s="4">
+        <v>72.40427160465541</v>
+      </c>
+      <c r="P13" s="5">
+        <v>5652</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1726,4 +2385,583 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>104</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>104</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>104</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>104</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>104</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>104</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>102</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>2</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>1</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>104</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>104</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>104</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>104</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/public/downloads/RolingConfigurational2017.xlsx
+++ b/public/downloads/RolingConfigurational2017.xlsx
@@ -1261,13 +1261,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.103021916988827</v>
+        <v>0.1005989086363357</v>
       </c>
       <c r="I3" s="4">
-        <v>0.103021916988827</v>
+        <v>0.1005989086363357</v>
       </c>
       <c r="J3" s="4">
-        <v>0.1060186066048415</v>
+        <v>0.1049615737171289</v>
       </c>
       <c r="K3" s="4">
         <v>86.07993197278911</v>
@@ -1311,13 +1311,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.1140993187405174</v>
+        <v>0.1112572368332909</v>
       </c>
       <c r="I4" s="4">
-        <v>0.1140993187405174</v>
+        <v>0.1112572368332909</v>
       </c>
       <c r="J4" s="4">
-        <v>0.1174083778488327</v>
+        <v>0.1156466066650382</v>
       </c>
       <c r="K4" s="4">
         <v>80.64887493458922</v>
@@ -1361,13 +1361,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.05831450248664646</v>
+        <v>0.05774538022553489</v>
       </c>
       <c r="I5" s="4">
-        <v>0.05831450248664646</v>
+        <v>0.05774538022553489</v>
       </c>
       <c r="J5" s="4">
-        <v>0.06160941940857922</v>
+        <v>0.06130283441841488</v>
       </c>
       <c r="K5" s="4">
         <v>85.13343799058082</v>
@@ -1411,13 +1411,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.1372351381088362</v>
+        <v>0.1357814276975879</v>
       </c>
       <c r="I6" s="4">
-        <v>0.1372351381088362</v>
+        <v>0.1357814276975879</v>
       </c>
       <c r="J6" s="4">
-        <v>0.1164844112913922</v>
+        <v>0.1162895868535269</v>
       </c>
       <c r="K6" s="4">
         <v>84.63108320251176</v>
@@ -1461,13 +1461,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.0478067333306197</v>
+        <v>0.04687695756587142</v>
       </c>
       <c r="I7" s="4">
-        <v>0.0478067333306197</v>
+        <v>0.04687695756587142</v>
       </c>
       <c r="J7" s="4">
-        <v>0.04939457123855819</v>
+        <v>0.04856542516489483</v>
       </c>
       <c r="K7" s="4">
         <v>88.9046964939822</v>
@@ -1511,13 +1511,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.09964046277429914</v>
+        <v>0.09690767885427592</v>
       </c>
       <c r="I8" s="4">
-        <v>0.09964046277429914</v>
+        <v>0.09690767885427592</v>
       </c>
       <c r="J8" s="4">
-        <v>0.1035194106231965</v>
+        <v>0.1023403012096705</v>
       </c>
       <c r="K8" s="4">
         <v>86.36087127158555</v>
@@ -1561,13 +1561,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.1095421811633829</v>
+        <v>0.1070501417518825</v>
       </c>
       <c r="I9" s="4">
-        <v>0.1077199527352652</v>
+        <v>0.1052336260459115</v>
       </c>
       <c r="J9" s="4">
-        <v>0.1015031107460929</v>
+        <v>0.1009769846691031</v>
       </c>
       <c r="K9" s="4">
         <v>86.20290423861852</v>
@@ -1611,13 +1611,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.08055680187672976</v>
+        <v>0.07922659438918471</v>
       </c>
       <c r="I10" s="4">
-        <v>0.08055680187672976</v>
+        <v>0.07922659438918471</v>
       </c>
       <c r="J10" s="4">
-        <v>0.07785016243543508</v>
+        <v>0.07682239533936074</v>
       </c>
       <c r="K10" s="4">
         <v>84.19250392464679</v>
@@ -1661,13 +1661,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.1319909119088531</v>
+        <v>0.1287227703516346</v>
       </c>
       <c r="I11" s="4">
-        <v>0.1319909119088531</v>
+        <v>0.1287227703516346</v>
       </c>
       <c r="J11" s="4">
-        <v>0.1383613676439696</v>
+        <v>0.1356971553415685</v>
       </c>
       <c r="K11" s="4">
         <v>86.07110151753011</v>
@@ -1711,13 +1711,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.08673320255060089</v>
+        <v>0.08542840203686528</v>
       </c>
       <c r="I12" s="4">
-        <v>0.08673320255060089</v>
+        <v>0.08542840203686528</v>
       </c>
       <c r="J12" s="4">
-        <v>0.08540929730643801</v>
+        <v>0.0842464974244021</v>
       </c>
       <c r="K12" s="4">
         <v>81.09399529042385</v>
@@ -1761,13 +1761,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.06454059049285941</v>
+        <v>0.06349033074889873</v>
       </c>
       <c r="I13" s="4">
-        <v>0.06454059049285941</v>
+        <v>0.06349033074889873</v>
       </c>
       <c r="J13" s="4">
-        <v>0.06561969954937533</v>
+        <v>0.06519168237916163</v>
       </c>
       <c r="K13" s="4">
         <v>87.70408163265306</v>
